--- a/artfynd/A 22080-2026 artfynd.xlsx
+++ b/artfynd/A 22080-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120491782</v>
+        <v>128582511</v>
       </c>
       <c r="B2" t="n">
-        <v>57298</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,20 +712,24 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossberga, Grytsjön, Kråksmåla, Sm</t>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547220</v>
+        <v>547246</v>
       </c>
       <c r="R2" t="n">
-        <v>6321964</v>
+        <v>6321894</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128582511</v>
+        <v>125030192</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102119</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,11 +831,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -846,17 +849,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Mossberga, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547246</v>
+        <v>547251</v>
       </c>
       <c r="R3" t="n">
-        <v>6321894</v>
+        <v>6321852</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +883,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,6 +922,248 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120491782</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mossberga, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321964</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128771373</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grönskåra, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547174</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6321957</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22080-2026 artfynd.xlsx
+++ b/artfynd/A 22080-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128582511</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125030192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120491782</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,8 +1184,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128771373</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>